--- a/src/nodes/HPC/compressor_stage_2_blade_stator_coordinates_lattice.xlsx
+++ b/src/nodes/HPC/compressor_stage_2_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>5.4772647780901229</v>
+        <v>5.504164254755243</v>
       </c>
       <c r="B1">
-        <v>8.641679369605054</v>
+        <v>8.6245711564714274</v>
       </c>
       <c r="C1">
         <v>190.54511692961938</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>4.8585146861158792</v>
+        <v>4.8847898465513975</v>
       </c>
       <c r="B2">
-        <v>8.4403467003742261</v>
+        <v>8.42516738900481</v>
       </c>
       <c r="C2">
         <v>190.54511692961938</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>4.3068162405988888</v>
+        <v>4.3322833441517989</v>
       </c>
       <c r="B3">
-        <v>8.18014857476403</v>
+        <v>8.1666895289024684</v>
       </c>
       <c r="C3">
         <v>190.54511692961938</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>3.7720396566843339</v>
+        <v>3.7966523326230406</v>
       </c>
       <c r="B4">
-        <v>7.9050945409301514</v>
+        <v>7.8933031069274762</v>
       </c>
       <c r="C4">
         <v>190.54511692961938</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>3.2512469396498886</v>
+        <v>3.2749668681870645</v>
       </c>
       <c r="B5">
-        <v>7.6177639001919077</v>
+        <v>7.6075965661913747</v>
       </c>
       <c r="C5">
         <v>190.54511692961938</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>2.743157748673597</v>
+        <v>2.7659501185212783</v>
       </c>
       <c r="B6">
-        <v>7.3192806793374219</v>
+        <v>7.3106979173593407</v>
       </c>
       <c r="C6">
         <v>190.54511692961938</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>2.2469932563132535</v>
+        <v>2.2688253903930029</v>
       </c>
       <c r="B7">
-        <v>7.0103286204557955</v>
+        <v>7.0032933259008185</v>
       </c>
       <c r="C7">
         <v>190.54511692961938</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>1.7622482389608885</v>
+        <v>1.7830888446511841</v>
       </c>
       <c r="B8">
-        <v>6.6913512655005523</v>
+        <v>6.6858279058107009</v>
       </c>
       <c r="C8">
         <v>190.54511692961938</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>1.288218962205522</v>
+        <v>1.3080386753180295</v>
       </c>
       <c r="B9">
-        <v>6.3629664314748693</v>
+        <v>6.3589216638148756</v>
       </c>
       <c r="C9">
         <v>190.54511692961938</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>0.82416154412789455</v>
+        <v>0.84293303892309879</v>
       </c>
       <c r="B10">
-        <v>6.0258271813679931</v>
+        <v>6.0232299775473015</v>
       </c>
       <c r="C10">
         <v>190.54511692961938</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>0.36937002357865678</v>
+        <v>0.38706790885212905</v>
       </c>
       <c r="B11">
-        <v>5.6805532870638142</v>
+        <v>5.679374815543242</v>
       </c>
       <c r="C11">
         <v>190.54511692961938</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-0.076567922617674145</v>
+        <v>-0.05996790818715543</v>
       </c>
       <c r="B12">
-        <v>5.3275067320956682</v>
+        <v>5.3277194443106994</v>
       </c>
       <c r="C12">
         <v>190.54511692961938</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-0.51292798651102933</v>
+        <v>-0.49745208905523997</v>
       </c>
       <c r="B13">
-        <v>4.9660516377000512</v>
+        <v>4.96762573134734</v>
       </c>
       <c r="C13">
         <v>190.54511692961938</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-0.93929977462090475</v>
+        <v>-0.92497536486691656</v>
       </c>
       <c r="B14">
-        <v>4.5958277144463375</v>
+        <v>4.5987321102522634</v>
       </c>
       <c r="C14">
         <v>190.54511692961938</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.357665182470633</v>
+        <v>-1.3445142001859971</v>
       </c>
       <c r="B15">
-        <v>4.21857489253223</v>
+        <v>4.22278467804061</v>
       </c>
       <c r="C15">
         <v>190.54511692961938</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.7698415856556453</v>
+        <v>-1.7578809904799624</v>
       </c>
       <c r="B16">
-        <v>3.8358886681086917</v>
+        <v>3.8413845857646103</v>
       </c>
       <c r="C16">
         <v>190.54511692961938</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.1745959910559858</v>
+        <v>-2.1638461213819968</v>
       </c>
       <c r="B17">
-        <v>3.4466865815113579</v>
+        <v>3.4534455372087889</v>
       </c>
       <c r="C17">
         <v>190.54511692961938</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-2.5703182005857004</v>
+        <v>-2.5608038072085764</v>
       </c>
       <c r="B18">
-        <v>3.0495550202459958</v>
+        <v>3.0575489096260955</v>
       </c>
       <c r="C18">
         <v>190.54511692961938</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-2.9569395650102432</v>
+        <v>-2.9486855868436561</v>
       </c>
       <c r="B19">
-        <v>2.6444337163142086</v>
+        <v>2.6536342214108606</v>
       </c>
       <c r="C19">
         <v>190.54511692961938</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-3.33477682230793</v>
+        <v>-3.3278073303130689</v>
       </c>
       <c r="B20">
-        <v>2.2316007378415517</v>
+        <v>2.2419805262427546</v>
       </c>
       <c r="C20">
         <v>190.54511692961938</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-3.7041467104570711</v>
+        <v>-3.6984849076426429</v>
       </c>
       <c r="B21">
-        <v>1.8113341529535842</v>
+        <v>1.8228668778014499</v>
       </c>
       <c r="C21">
         <v>190.54511692961938</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.0653073470310259</v>
+        <v>-4.0609757290899022</v>
       </c>
       <c r="B22">
-        <v>1.3838605662090049</v>
+        <v>1.3965206837979476</v>
       </c>
       <c r="C22">
         <v>190.54511692961938</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-4.4182823679833518</v>
+        <v>-4.415303365839141</v>
       </c>
       <c r="B23">
-        <v>0.94920072789906662</v>
+        <v>0.962962768068554</v>
       </c>
       <c r="C23">
         <v>190.54511692961938</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-4.7630367888626539</v>
+        <v>-4.7614329293063484</v>
       </c>
       <c r="B24">
-        <v>0.5073239247481609</v>
+        <v>0.52216230848090017</v>
       </c>
       <c r="C24">
         <v>190.54511692961938</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.0995356252175332</v>
+        <v>-5.0993295309075117</v>
       </c>
       <c r="B25">
-        <v>0.058199443480681963</v>
+        <v>0.07408848290262017</v>
       </c>
       <c r="C25">
         <v>190.54511692961938</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-5.4277301275212722</v>
+        <v>-5.4289445547035324</v>
       </c>
       <c r="B26">
-        <v>-0.39821551370611147</v>
+        <v>-0.3813016581568564</v>
       </c>
       <c r="C26">
         <v>190.54511692961938</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-5.7475164859458516</v>
+        <v>-5.7501744753349557</v>
       </c>
       <c r="B27">
-        <v>-0.86201208272350693</v>
+        <v>-0.84409957362092858</v>
       </c>
       <c r="C27">
         <v>190.54511692961938</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-6.0587771255879268</v>
+        <v>-6.062902040087236</v>
       </c>
       <c r="B28">
-        <v>-1.333293484009924</v>
+        <v>-1.3144088497711983</v>
       </c>
       <c r="C28">
         <v>190.54511692961938</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-6.3613944715441555</v>
+        <v>-6.3670099962458329</v>
       </c>
       <c r="B29">
-        <v>-1.8121629380037831</v>
+        <v>-1.7923330728892677</v>
       </c>
       <c r="C29">
         <v>190.54511692961938</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-6.6552854590617789</v>
+        <v>-6.6624155066791211</v>
       </c>
       <c r="B30">
-        <v>-2.2986933682623447</v>
+        <v>-2.2779454249946407</v>
       </c>
       <c r="C30">
         <v>190.54511692961938</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-6.94050506399039</v>
+        <v>-6.949173396587172</v>
       </c>
       <c r="B31">
-        <v>-2.79283651081825</v>
+        <v>-2.7711974710584557</v>
       </c>
       <c r="C31">
         <v>190.54511692961938</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-7.2171427723301678</v>
+        <v>-7.2273729067529811</v>
       </c>
       <c r="B32">
-        <v>-3.2945138048229872</v>
+        <v>-3.2720103717897606</v>
       </c>
       <c r="C32">
         <v>190.54511692961938</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-7.4852880700812907</v>
+        <v>-7.4971032779595363</v>
       </c>
       <c r="B33">
-        <v>-3.8036466894280321</v>
+        <v>-3.7803052878975913</v>
       </c>
       <c r="C33">
         <v>190.54511692961938</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-7.7449589210573393</v>
+        <v>-7.7583824247944424</v>
       </c>
       <c r="B34">
-        <v>-4.3202193939828479</v>
+        <v>-4.2960663928356508</v>
       </c>
       <c r="C34">
         <v>190.54511692961938</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-7.9958872003254928</v>
+        <v>-8.0109429570637332</v>
       </c>
       <c r="B35">
-        <v>-4.8444673086287828</v>
+        <v>-4.8195299110362386</v>
       </c>
       <c r="C35">
         <v>190.54511692961938</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-8.237733260766321</v>
+        <v>-8.2544461583780571</v>
       </c>
       <c r="B36">
-        <v>-5.3766886137051539</v>
+        <v>-5.3509950796763111</v>
       </c>
       <c r="C36">
         <v>190.54511692961938</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-8.4701574552604058</v>
+        <v>-8.4885533123480563</v>
       </c>
       <c r="B37">
-        <v>-5.9171814895512886</v>
+        <v>-5.8907611359328325</v>
       </c>
       <c r="C37">
         <v>190.54511692961938</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-8.69265395738946</v>
+        <v>-8.7127599786642378</v>
       </c>
       <c r="B38">
-        <v>-6.4663900073352307</v>
+        <v>-6.4392737248908993</v>
       </c>
       <c r="C38">
         <v>190.54511692961938</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-8.9040522235397273</v>
+        <v>-8.9258988213365047</v>
       </c>
       <c r="B39">
-        <v>-7.0253418015398834</v>
+        <v>-6.9975641232681838</v>
       </c>
       <c r="C39">
         <v>190.54511692961938</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-9.1030155307985936</v>
+        <v>-9.1266367804546267</v>
       </c>
       <c r="B40">
-        <v>-7.595210397476885</v>
+        <v>-7.5668100156905078</v>
       </c>
       <c r="C40">
         <v>190.54511692961938</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-9.2882071562534332</v>
+        <v>-9.31364079610837</v>
       </c>
       <c r="B41">
-        <v>-8.1771693204578639</v>
+        <v>-8.14818908678368</v>
       </c>
       <c r="C41">
         <v>190.54511692961938</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-9.2882071562534332</v>
+        <v>-9.31364079610837</v>
       </c>
       <c r="B42">
-        <v>-8.1771693204578639</v>
+        <v>-8.14818908678368</v>
       </c>
       <c r="C42">
         <v>190.54511692961938</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-9.0476536308548869</v>
+        <v>-9.0714265879213229</v>
       </c>
       <c r="B43">
-        <v>-7.6438132831389529</v>
+        <v>-7.615585164080775</v>
       </c>
       <c r="C43">
         <v>190.54511692961938</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-8.8028363921229289</v>
+        <v>-8.824960350192594</v>
       </c>
       <c r="B44">
-        <v>-7.1142004116407627</v>
+        <v>-7.0867376740642811</v>
       </c>
       <c r="C44">
         <v>190.54511692961938</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-8.5527490240415371</v>
+        <v>-8.5732384247733489</v>
       </c>
       <c r="B45">
-        <v>-6.58921425083089</v>
+        <v>-6.5625332931411577</v>
       </c>
       <c r="C45">
         <v>190.54511692961938</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-8.2963851105946755</v>
+        <v>-8.3152571535147448</v>
       </c>
       <c r="B46">
-        <v>-6.0697383455769263</v>
+        <v>-6.0438586977183544</v>
       </c>
       <c r="C46">
         <v>190.54511692961938</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-8.03288901818271</v>
+        <v>-8.0501632474974762</v>
       </c>
       <c r="B47">
-        <v>-5.5565238670282424</v>
+        <v>-5.5314677213137342</v>
       </c>
       <c r="C47">
         <v>190.54511692961938</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-7.7620082428715858</v>
+        <v>-7.7777048947203511</v>
       </c>
       <c r="B48">
-        <v>-5.0497924914612753</v>
+        <v>-5.0255828258887743</v>
       </c>
       <c r="C48">
         <v>190.54511692961938</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.4836410631436392</v>
+        <v>-7.4977806524117039</v>
       </c>
       <c r="B49">
-        <v>-4.5496335214342256</v>
+        <v>-4.5262936305158536</v>
       </c>
       <c r="C49">
         <v>190.54511692961938</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.1976857574812154</v>
+        <v>-7.2102890777998745</v>
       </c>
       <c r="B50">
-        <v>-4.0561362595053074</v>
+        <v>-4.0336897542673595</v>
       </c>
       <c r="C50">
         <v>190.54511692961938</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-6.9040982824735853</v>
+        <v>-6.9151862481656545</v>
       </c>
       <c r="B51">
-        <v>-3.5693393719207656</v>
+        <v>-3.5478100004339339</v>
       </c>
       <c r="C51">
         <v>190.54511692961938</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-6.603065307137741</v>
+        <v>-6.6126583209996408</v>
       </c>
       <c r="B52">
-        <v>-3.0890789796789928</v>
+        <v>-3.0684899091792412</v>
       </c>
       <c r="C52">
         <v>190.54511692961938</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.2948311785976063</v>
+        <v>-6.3029489738448827</v>
       </c>
       <c r="B53">
-        <v>-2.6151405674664319</v>
+        <v>-2.5955142048852125</v>
       </c>
       <c r="C53">
         <v>190.54511692961938</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-5.9796402439771077</v>
+        <v>-5.9863018842444289</v>
       </c>
       <c r="B54">
-        <v>-2.147309619969513</v>
+        <v>-2.12866761193377</v>
       </c>
       <c r="C54">
         <v>190.54511692961938</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-5.6576912923182912</v>
+        <v>-5.662915296501601</v>
       </c>
       <c r="B55">
-        <v>-1.6854116178691476</v>
+        <v>-1.6677749924587224</v>
       </c>
       <c r="C55">
         <v>190.54511692961938</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.3290008803357125</v>
+        <v>-5.332805721960832</v>
       </c>
       <c r="B56">
-        <v>-1.229432025824154</v>
+        <v>-1.2128217596014224</v>
       </c>
       <c r="C56">
         <v>190.54511692961938</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-4.9935400066620481</v>
+        <v>-4.995944238726822</v>
       </c>
       <c r="B57">
-        <v>-0.77939630448782071</v>
+        <v>-0.763833464255102</v>
       </c>
       <c r="C57">
         <v>190.54511692961938</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-4.651279669929977</v>
+        <v>-4.6523019249042772</v>
       </c>
       <c r="B58">
-        <v>-0.33532991451344207</v>
+        <v>-0.32083565731299635</v>
       </c>
       <c r="C58">
         <v>190.54511692961938</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.3021947319560487</v>
+        <v>-4.3018537111955455</v>
       </c>
       <c r="B59">
-        <v>0.10274507498182892</v>
+        <v>0.11614951388838699</v>
       </c>
       <c r="C59">
         <v>190.54511692961938</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-3.946275507292313</v>
+        <v>-3.9445899386935692</v>
       </c>
       <c r="B60">
-        <v>0.534820161025373</v>
+        <v>0.54711351623942672</v>
       </c>
       <c r="C60">
         <v>190.54511692961938</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.583516173674695</v>
+        <v>-3.5805048010889391</v>
       </c>
       <c r="B61">
-        <v>0.96089023218070424</v>
+        <v>0.9720512201872229</v>
       </c>
       <c r="C61">
         <v>190.54511692961938</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.2139109088391171</v>
+        <v>-3.2095924920722432</v>
       </c>
       <c r="B62">
-        <v>1.3809501770113384</v>
+        <v>1.3909574961788771</v>
       </c>
       <c r="C62">
         <v>190.54511692961938</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-2.8375025848702276</v>
+        <v>-2.8318957662463795</v>
       </c>
       <c r="B63">
-        <v>1.7950376334421014</v>
+        <v>1.8038701155389418</v>
       </c>
       <c r="C63">
         <v>190.54511692961938</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.4545288512475771</v>
+        <v>-2.44765162186348</v>
       </c>
       <c r="B64">
-        <v>2.2033612368430586</v>
+        <v>2.2109984531017655</v>
       </c>
       <c r="C64">
         <v>190.54511692961938</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.0652760517994433</v>
+        <v>-2.057145618087989</v>
       </c>
       <c r="B65">
-        <v>2.6061723719455823</v>
+        <v>2.6125947845791444</v>
       </c>
       <c r="C65">
         <v>190.54511692961938</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.6700305303540985</v>
+        <v>-1.6606633140843439</v>
       </c>
       <c r="B66">
-        <v>3.0037224234810513</v>
+        <v>3.0089113856828811</v>
       </c>
       <c r="C66">
         <v>190.54511692961938</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.2686850635999269</v>
+        <v>-1.2580977803634135</v>
       </c>
       <c r="B67">
-        <v>3.3959172587993867</v>
+        <v>3.3998537901294728</v>
       </c>
       <c r="C67">
         <v>190.54511692961938</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.85955815966572924</v>
+        <v>-0.84777213282175345</v>
       </c>
       <c r="B68">
-        <v>3.7812806757247106</v>
+        <v>3.7839405636542329</v>
       </c>
       <c r="C68">
         <v>190.54511692961938</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.44133343170572337</v>
+        <v>-0.42837359188933649</v>
       </c>
       <c r="B69">
-        <v>4.1586570022259446</v>
+        <v>4.1600119381891023</v>
       </c>
       <c r="C69">
         <v>190.54511692961938</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.015729181535389502</v>
+        <v>-0.0016157507441321752</v>
       </c>
       <c r="B70">
-        <v>4.5295547563769869</v>
+        <v>4.5295817784337107</v>
       </c>
       <c r="C70">
         <v>190.54511692961938</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>0.41538160676869457</v>
+        <v>0.43063353904834389</v>
       </c>
       <c r="B71">
-        <v>4.895618253691099</v>
+        <v>4.8943002278325682</v>
       </c>
       <c r="C71">
         <v>190.54511692961938</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.85254190874678448</v>
+        <v>0.86891576512036206</v>
       </c>
       <c r="B72">
-        <v>5.2563708093339923</v>
+        <v>5.2536889120420325</v>
       </c>
       <c r="C72">
         <v>190.54511692961938</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>1.2966205168360241</v>
+        <v>1.3140973391697659</v>
       </c>
       <c r="B73">
-        <v>5.6110496998527246</v>
+        <v>5.6069824042959509</v>
       </c>
       <c r="C73">
         <v>190.54511692961938</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.7473735314442394</v>
+        <v>1.7659350299588936</v>
       </c>
       <c r="B74">
-        <v>5.95986904766729</v>
+        <v>5.9543955859262994</v>
       </c>
       <c r="C74">
         <v>190.54511692961938</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2.2042760336966323</v>
+        <v>2.2239053570405152</v>
       </c>
       <c r="B75">
-        <v>6.3032896854456348</v>
+        <v>6.2963909229257027</v>
       </c>
       <c r="C75">
         <v>190.54511692961938</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.6667917196172244</v>
+        <v>2.6874734860646505</v>
       </c>
       <c r="B76">
-        <v>6.6417824409745814</v>
+        <v>6.6334409118312623</v>
       </c>
       <c r="C76">
         <v>190.54511692961938</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>3.1344388824530904</v>
+        <v>3.1561590302923923</v>
       </c>
       <c r="B77">
-        <v>6.9757702104744306</v>
+        <v>6.9659699477301826</v>
       </c>
       <c r="C77">
         <v>190.54511692961938</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>3.606965589444719</v>
+        <v>3.6297107473319103</v>
       </c>
       <c r="B78">
-        <v>7.3054741687805409</v>
+        <v>7.2941999893656089</v>
       </c>
       <c r="C78">
         <v>190.54511692961938</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>4.0838611113981</v>
+        <v>4.10761930753299</v>
       </c>
       <c r="B79">
-        <v>7.6313426912674212</v>
+        <v>7.6185810012844639</v>
       </c>
       <c r="C79">
         <v>190.54511692961938</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>4.5641446255568514</v>
+        <v>4.5889065758736027</v>
       </c>
       <c r="B80">
-        <v>7.9542368541685722</v>
+        <v>7.9399771116242555</v>
       </c>
       <c r="C80">
         <v>190.54511692961938</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>5.0452039065755772</v>
+        <v>5.0709674852515292</v>
       </c>
       <c r="B81">
-        <v>8.2764499619030119</v>
+        <v>8.2606897529402232</v>
       </c>
       <c r="C81">
         <v>190.54511692961938</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5.4772647780901229</v>
+        <v>5.504164254755243</v>
       </c>
       <c r="B82">
-        <v>8.641679369605054</v>
+        <v>8.6245711564714274</v>
       </c>
       <c r="C82">
         <v>190.54511692961938</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>5.4556827084941775</v>
+        <v>5.5101667241998555</v>
       </c>
       <c r="B1">
-        <v>9.9335266167900542</v>
+        <v>9.9034078747550058</v>
       </c>
       <c r="C1">
         <v>230.80559063164714</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>4.7163671501231681</v>
+        <v>4.7334658141671309</v>
       </c>
       <c r="B2">
-        <v>9.719792439995361</v>
+        <v>9.7218980339254522</v>
       </c>
       <c r="C2">
         <v>230.80559063164714</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>4.1004486376595874</v>
+        <v>4.1021557210987378</v>
       </c>
       <c r="B3">
-        <v>9.4112101788676483</v>
+        <v>9.42735887292504</v>
       </c>
       <c r="C3">
         <v>230.80559063164714</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>3.5103984022130392</v>
+        <v>3.4997370430783006</v>
       </c>
       <c r="B4">
-        <v>9.0827444877759547</v>
+        <v>9.1103590292637282</v>
       </c>
       <c r="C4">
         <v>230.80559063164714</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2.9406285844406619</v>
+        <v>2.9195687153365379</v>
       </c>
       <c r="B5">
-        <v>8.7386904270298444</v>
+        <v>8.77606138084368</v>
       </c>
       <c r="C5">
         <v>230.80559063164714</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>2.3887700957526703</v>
+        <v>2.3588529649878032</v>
       </c>
       <c r="B6">
-        <v>8.3808689763189275</v>
+        <v>8.4266409643959665</v>
       </c>
       <c r="C6">
         <v>230.80559063164714</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>1.8534177064952901</v>
+        <v>1.8159403102081924</v>
       </c>
       <c r="B7">
-        <v>8.0103602534023342</v>
+        <v>8.0633801154427474</v>
       </c>
       <c r="C7">
         <v>230.80559063164714</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>1.3336930334646719</v>
+        <v>1.2898091823155049</v>
       </c>
       <c r="B8">
-        <v>7.6278394200198214</v>
+        <v>7.6870730190368892</v>
       </c>
       <c r="C8">
         <v>230.80559063164714</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>0.828317672387445</v>
+        <v>0.7789565884990346</v>
       </c>
       <c r="B9">
-        <v>7.2342891106861806</v>
+        <v>7.2988881276237585</v>
       </c>
       <c r="C9">
         <v>230.80559063164714</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>0.33592889393058678</v>
+        <v>0.28177718532782642</v>
       </c>
       <c r="B10">
-        <v>6.8307567756523566</v>
+        <v>6.9000734627801679</v>
       </c>
       <c r="C10">
         <v>230.80559063164714</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-0.14477331040803257</v>
+        <v>-0.20326234898158979</v>
       </c>
       <c r="B11">
-        <v>6.418241655338873</v>
+        <v>6.4918210552162208</v>
       </c>
       <c r="C11">
         <v>230.80559063164714</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-0.61452209515275125</v>
+        <v>-0.67701938614407686</v>
       </c>
       <c r="B12">
-        <v>5.9973072827026321</v>
+        <v>6.0747974404400589</v>
       </c>
       <c r="C12">
         <v>230.80559063164714</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.0718459197476367</v>
+        <v>-1.1377195192475462</v>
       </c>
       <c r="B13">
-        <v>5.5668225706765018</v>
+        <v>5.64762316401868</v>
       </c>
       <c r="C13">
         <v>230.80559063164714</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.5158898924473716</v>
+        <v>-1.5843265013072292</v>
       </c>
       <c r="B14">
-        <v>5.1261304140294843</v>
+        <v>5.2094926297345019</v>
       </c>
       <c r="C14">
         <v>230.80559063164714</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.9504704118294027</v>
+        <v>-2.0213885036745887</v>
       </c>
       <c r="B15">
-        <v>4.6781642548991922</v>
+        <v>4.7639416641727905</v>
       </c>
       <c r="C15">
         <v>230.80559063164714</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.3790874170935004</v>
+        <v>-2.4530766459704423</v>
       </c>
       <c r="B16">
-        <v>4.2256142916282151</v>
+        <v>4.3142129674224279</v>
       </c>
       <c r="C16">
         <v>230.80559063164714</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.7993037196059958</v>
+        <v>-2.876469422556827</v>
       </c>
       <c r="B17">
-        <v>3.7666072000104327</v>
+        <v>3.8580353107839032</v>
       </c>
       <c r="C17">
         <v>230.80559063164714</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-3.2079521827887545</v>
+        <v>-3.2877744459736773</v>
       </c>
       <c r="B18">
-        <v>3.2987085875930293</v>
+        <v>3.3924604270599779</v>
       </c>
       <c r="C18">
         <v>230.80559063164714</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.6048830061192438</v>
+        <v>-3.6868084267313126</v>
       </c>
       <c r="B19">
-        <v>2.8218033114851062</v>
+        <v>2.9173458238508903</v>
       </c>
       <c r="C19">
         <v>230.80559063164714</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-3.9907007230888318</v>
+        <v>-4.0742903498326548</v>
       </c>
       <c r="B20">
-        <v>2.3363560411862396</v>
+        <v>2.4332504524562428</v>
       </c>
       <c r="C20">
         <v>230.80559063164714</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-4.366009867188887</v>
+        <v>-4.4509392002806178</v>
       </c>
       <c r="B21">
-        <v>1.8428314461960134</v>
+        <v>1.9407332641756445</v>
       </c>
       <c r="C21">
         <v>230.80559063164714</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.7313048750194842</v>
+        <v>-4.8173435109280645</v>
       </c>
       <c r="B22">
-        <v>1.3416095709798019</v>
+        <v>1.4402517945649518</v>
       </c>
       <c r="C22">
         <v>230.80559063164714</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.0866397956155271</v>
+        <v>-5.1735700060276013</v>
       </c>
       <c r="B23">
-        <v>0.83273195986618453</v>
+        <v>0.93185791620504121</v>
       </c>
       <c r="C23">
         <v>230.80559063164714</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-5.43195858112062</v>
+        <v>-5.5195549576817768</v>
       </c>
       <c r="B24">
-        <v>0.31615553214953473</v>
+        <v>0.41550208593303967</v>
       </c>
       <c r="C24">
         <v>230.80559063164714</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-5.7672051836783753</v>
+        <v>-5.85523463799314</v>
       </c>
       <c r="B25">
-        <v>-0.20816279287577069</v>
+        <v>-0.10886523941392237</v>
       </c>
       <c r="C25">
         <v>230.80559063164714</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.0923008557269771</v>
+        <v>-6.1805192952170325</v>
       </c>
       <c r="B26">
-        <v>-0.74028354384985062</v>
+        <v>-0.64131383438484391</v>
       </c>
       <c r="C26">
         <v>230.80559063164714</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-6.4070760508829272</v>
+        <v>-6.49521508221999</v>
       </c>
       <c r="B27">
-        <v>-1.2803370411508266</v>
+        <v>-1.1819943990732489</v>
       </c>
       <c r="C27">
         <v>230.80559063164714</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-6.7113385230572966</v>
+        <v>-6.7991021280213344</v>
       </c>
       <c r="B28">
-        <v>-1.8284710530913064</v>
+        <v>-1.7310778649587806</v>
       </c>
       <c r="C28">
         <v>230.80559063164714</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-7.00489602616116</v>
+        <v>-7.091960561640394</v>
       </c>
       <c r="B29">
-        <v>-2.3848333479839039</v>
+        <v>-2.2887351635210877</v>
       </c>
       <c r="C29">
         <v>230.80559063164714</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-7.2876281750763594</v>
+        <v>-7.3736576038303987</v>
       </c>
       <c r="B30">
-        <v>-2.949516458820439</v>
+        <v>-2.8550695196288949</v>
       </c>
       <c r="C30">
         <v>230.80559063164714</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-7.559702028567802</v>
+        <v>-7.6444088422801872</v>
       </c>
       <c r="B31">
-        <v>-3.5223919773095576</v>
+        <v>-3.4299133317072492</v>
       </c>
       <c r="C31">
         <v>230.80559063164714</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-7.8213565063711634</v>
+        <v>-7.90451695641251</v>
       </c>
       <c r="B32">
-        <v>-4.1032762598391264</v>
+        <v>-4.01303129157028</v>
       </c>
       <c r="C32">
         <v>230.80559063164714</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-8.0728305282221182</v>
+        <v>-8.15428462565011</v>
       </c>
       <c r="B33">
-        <v>-4.6919856627969967</v>
+        <v>-4.60418809103211</v>
       </c>
       <c r="C33">
         <v>230.80559063164714</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-8.3142294823338148</v>
+        <v>-8.3938564955866237</v>
       </c>
       <c r="B34">
-        <v>-5.2884391804341693</v>
+        <v>-5.2032712801219922</v>
       </c>
       <c r="C34">
         <v>230.80559063164714</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-8.54512463082931</v>
+        <v>-8.622745076499255</v>
       </c>
       <c r="B35">
-        <v>-5.8929663584541885</v>
+        <v>-5.8106598417296924</v>
       </c>
       <c r="C35">
         <v>230.80559063164714</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-8.76495370430913</v>
+        <v>-8.8403048448360941</v>
       </c>
       <c r="B36">
-        <v>-6.50599938042374</v>
+        <v>-6.4268556169600926</v>
       </c>
       <c r="C36">
         <v>230.80559063164714</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-8.97315443337381</v>
+        <v>-9.0458902770452383</v>
       </c>
       <c r="B37">
-        <v>-7.1279704299095137</v>
+        <v>-7.0523604469180938</v>
       </c>
       <c r="C37">
         <v>230.80559063164714</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-9.1688472848251443</v>
+        <v>-9.2384784315402886</v>
       </c>
       <c r="B38">
-        <v>-7.75955555258459</v>
+        <v>-7.6879695839758773</v>
       </c>
       <c r="C38">
         <v>230.80559063164714</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-9.3498836702699872</v>
+        <v>-9.41553669459687</v>
       </c>
       <c r="B39">
-        <v>-8.4024062425476451</v>
+        <v>-8.335651925574826</v>
       </c>
       <c r="C39">
         <v>230.80559063164714</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-9.5137977375164624</v>
+        <v>-9.57415503445611</v>
       </c>
       <c r="B40">
-        <v>-9.0584178560037465</v>
+        <v>-8.99766978042362</v>
       </c>
       <c r="C40">
         <v>230.80559063164714</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-9.6581236343726911</v>
+        <v>-9.7114234193591429</v>
       </c>
       <c r="B41">
-        <v>-9.7294857491579609</v>
+        <v>-9.6762854572309376</v>
       </c>
       <c r="C41">
         <v>230.80559063164714</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-9.6581236343726911</v>
+        <v>-9.7114234193591429</v>
       </c>
       <c r="B42">
-        <v>-9.7294857491579609</v>
+        <v>-9.6762854572309376</v>
       </c>
       <c r="C42">
         <v>230.80559063164714</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-9.40592454682271</v>
+        <v>-9.4452557211738259</v>
       </c>
       <c r="B43">
-        <v>-9.1413336617505774</v>
+        <v>-9.0978783221664017</v>
       </c>
       <c r="C43">
         <v>230.80559063164714</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-9.1526636562395289</v>
+        <v>-9.1798755056530883</v>
       </c>
       <c r="B44">
-        <v>-8.5539977201665991</v>
+        <v>-8.5188589845427014</v>
       </c>
       <c r="C44">
         <v>230.80559063164714</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-8.8962411862378</v>
+        <v>-8.9127372656538615</v>
       </c>
       <c r="B45">
-        <v>-7.9690918995722324</v>
+        <v>-7.9412063653665346</v>
       </c>
       <c r="C45">
         <v>230.80559063164714</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-8.6345573604321864</v>
+        <v>-8.6412954940330824</v>
       </c>
       <c r="B46">
-        <v>-7.388230175133681</v>
+        <v>-7.3668993856445963</v>
       </c>
       <c r="C46">
         <v>230.80559063164714</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-8.3658127415674741</v>
+        <v>-8.36336524872929</v>
       </c>
       <c r="B47">
-        <v>-6.812795668912571</v>
+        <v>-6.7976366568915285</v>
       </c>
       <c r="C47">
         <v>230.80559063164714</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-8.0894092489089982</v>
+        <v>-8.07820384800748</v>
       </c>
       <c r="B48">
-        <v>-6.2432480905522167</v>
+        <v>-6.2339955526537816</v>
       </c>
       <c r="C48">
         <v>230.80559063164714</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.8050491408522165</v>
+        <v>-7.7854291752142437</v>
       </c>
       <c r="B49">
-        <v>-5.6798162965913495</v>
+        <v>-5.6762731369857464</v>
       </c>
       <c r="C49">
         <v>230.80559063164714</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.5124346757925995</v>
+        <v>-7.4846591136961909</v>
       </c>
       <c r="B50">
-        <v>-5.1227291435687032</v>
+        <v>-5.1247664739418273</v>
       </c>
       <c r="C50">
         <v>230.80559063164714</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.2113863286087705</v>
+        <v>-7.17565433048482</v>
       </c>
       <c r="B51">
-        <v>-4.572124621933944</v>
+        <v>-4.5796616250855271</v>
       </c>
       <c r="C51">
         <v>230.80559063164714</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-6.9021974401119994</v>
+        <v>-6.8587466273512465</v>
       </c>
       <c r="B52">
-        <v>-4.0277772577804551</v>
+        <v>-4.0407006420167777</v>
       </c>
       <c r="C52">
         <v>230.80559063164714</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.5852795675967171</v>
+        <v>-6.5344105897514888</v>
       </c>
       <c r="B53">
-        <v>-3.4893707111125574</v>
+        <v>-3.5075145738446207</v>
       </c>
       <c r="C53">
         <v>230.80559063164714</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.2610442683573471</v>
+        <v>-6.2031208031415614</v>
       </c>
       <c r="B54">
-        <v>-2.9565886419345575</v>
+        <v>-2.9797344696780916</v>
       </c>
       <c r="C54">
         <v>230.80559063164714</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-5.9298189469435618</v>
+        <v>-5.8652525215541118</v>
       </c>
       <c r="B55">
-        <v>-2.4291793935385564</v>
+        <v>-2.4570686005821227</v>
       </c>
       <c r="C55">
         <v>230.80559063164714</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.5915943969259905</v>
+        <v>-5.5207836733283226</v>
       </c>
       <c r="B56">
-        <v>-1.9071500423677787</v>
+        <v>-1.9395341254452183</v>
       </c>
       <c r="C56">
         <v>230.80559063164714</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.2462772591305</v>
+        <v>-5.1695928553800012</v>
       </c>
       <c r="B57">
-        <v>-1.3905723481532286</v>
+        <v>-1.4272254251117751</v>
       </c>
       <c r="C57">
         <v>230.80559063164714</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-4.8937741743829646</v>
+        <v>-4.8115586646249611</v>
       </c>
       <c r="B58">
-        <v>-0.87951807062591669</v>
+        <v>-0.92023688042619123</v>
       </c>
       <c r="C58">
         <v>230.80559063164714</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.5340034326352061</v>
+        <v>-4.446574718071906</v>
       </c>
       <c r="B59">
-        <v>-0.37405001551577</v>
+        <v>-0.41865119535446649</v>
       </c>
       <c r="C59">
         <v>230.80559063164714</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.1669299203428967</v>
+        <v>-4.0745947131011295</v>
       </c>
       <c r="B60">
-        <v>0.12580482745156796</v>
+        <v>0.077495633650959087</v>
       </c>
       <c r="C60">
         <v>230.80559063164714</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.7925301730876622</v>
+        <v>-3.69558736718582</v>
       </c>
       <c r="B61">
-        <v>0.62002842255152779</v>
+        <v>0.56817928701603948</v>
       </c>
       <c r="C61">
         <v>230.80559063164714</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.4107807264511325</v>
+        <v>-3.3095213977991662</v>
       </c>
       <c r="B62">
-        <v>1.1086027340595408</v>
+        <v>1.0533754451667294</v>
       </c>
       <c r="C62">
         <v>230.80559063164714</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.0217571229459361</v>
+        <v>-2.9164849315961514</v>
       </c>
       <c r="B63">
-        <v>1.5915858270820742</v>
+        <v>1.533152619279383</v>
       </c>
       <c r="C63">
         <v>230.80559063164714</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.6259309328086973</v>
+        <v>-2.5170437319589296</v>
       </c>
       <c r="B64">
-        <v>2.0693401700497449</v>
+        <v>2.0079506435319652</v>
       </c>
       <c r="C64">
         <v>230.80559063164714</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.2238727332070423</v>
+        <v>-2.1118829714514535</v>
       </c>
       <c r="B65">
-        <v>2.5423043322241985</v>
+        <v>2.4783021828528367</v>
       </c>
       <c r="C65">
         <v>230.80559063164714</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.8161531013085952</v>
+        <v>-1.7016878226376715</v>
       </c>
       <c r="B66">
-        <v>3.01091688286709</v>
+        <v>2.9447399021703635</v>
       </c>
       <c r="C66">
         <v>230.80559063164714</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.402579148300279</v>
+        <v>-1.2862320903174589</v>
       </c>
       <c r="B67">
-        <v>3.4750295596413787</v>
+        <v>3.4070879534479919</v>
       </c>
       <c r="C67">
         <v>230.80559063164714</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.97990412144620875</v>
+        <v>-0.86164410823439752</v>
       </c>
       <c r="B68">
-        <v>3.9321467738152838</v>
+        <v>3.8623364367895041</v>
       </c>
       <c r="C68">
         <v>230.80559063164714</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.54559771817265768</v>
+        <v>-0.42490965136667092</v>
       </c>
       <c r="B69">
-        <v>4.3803236299487578</v>
+        <v>4.3081420418526752</v>
       </c>
       <c r="C69">
         <v>230.80559063164714</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.10304930047737781</v>
+        <v>0.019910269312790538</v>
       </c>
       <c r="B70">
-        <v>4.8221653321634514</v>
+        <v>4.7476618683708969</v>
       </c>
       <c r="C70">
         <v>230.80559063164714</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>0.34404626050622616</v>
+        <v>0.46838849494244567</v>
       </c>
       <c r="B71">
-        <v>5.2605119115661392</v>
+        <v>5.184337665739748</v>
       </c>
       <c r="C71">
         <v>230.80559063164714</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.79669172167355862</v>
+        <v>0.921708511100995</v>
       </c>
       <c r="B72">
-        <v>5.6945926076424067</v>
+        <v>5.617249371927894</v>
       </c>
       <c r="C72">
         <v>230.80559063164714</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>1.2565197137857578</v>
+        <v>1.3818051323104081</v>
       </c>
       <c r="B73">
-        <v>6.1231525127161541</v>
+        <v>6.04489282886923</v>
       </c>
       <c r="C73">
         <v>230.80559063164714</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.7229847350380798</v>
+        <v>1.8480078444254671</v>
       </c>
       <c r="B74">
-        <v>6.5466109220857378</v>
+        <v>6.4677893057854376</v>
       </c>
       <c r="C74">
         <v>230.80559063164714</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2.1949884124518708</v>
+        <v>2.3189841067862131</v>
       </c>
       <c r="B75">
-        <v>6.9658120907504788</v>
+        <v>6.8869747426900618</v>
       </c>
       <c r="C75">
         <v>230.80559063164714</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.6713990209187282</v>
+        <v>2.7933586013409308</v>
       </c>
       <c r="B76">
-        <v>7.3816259095390739</v>
+        <v>7.3035183354762818</v>
       </c>
       <c r="C76">
         <v>230.80559063164714</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>3.1511851212843185</v>
+        <v>3.2698742539207011</v>
       </c>
       <c r="B77">
-        <v>7.7948451853390424</v>
+        <v>7.7183973552103433</v>
       </c>
       <c r="C77">
         <v>230.80559063164714</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>3.6337497703403292</v>
+        <v>3.7477897432795428</v>
       </c>
       <c r="B78">
-        <v>8.2059287534437857</v>
+        <v>8.1321881177711344</v>
       </c>
       <c r="C78">
         <v>230.80559063164714</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>4.1179854843208332</v>
+        <v>4.22575207182834</v>
       </c>
       <c r="B79">
-        <v>8.6157278717813686</v>
+        <v>8.545942466740561</v>
       </c>
       <c r="C79">
         <v>230.80559063164714</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>4.601855452991261</v>
+        <v>4.7012943370575071</v>
       </c>
       <c r="B80">
-        <v>9.0258081171245426</v>
+        <v>8.9615782145321354</v>
       </c>
       <c r="C80">
         <v>230.80559063164714</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>5.080132878893207</v>
+        <v>5.1681350061372182</v>
       </c>
       <c r="B81">
-        <v>9.4401870226523243</v>
+        <v>9.3839787327384414</v>
       </c>
       <c r="C81">
         <v>230.80559063164714</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5.4556827084941775</v>
+        <v>5.5101667241998555</v>
       </c>
       <c r="B82">
-        <v>9.9335266167900542</v>
+        <v>9.9034078747550058</v>
       </c>
       <c r="C82">
         <v>230.80559063164714</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>5.4322498988055763</v>
+        <v>5.5052051078294371</v>
       </c>
       <c r="B1">
-        <v>10.99760200186067</v>
+        <v>10.961283488514393</v>
       </c>
       <c r="C1">
         <v>265.01886677730067</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>4.566890010077894</v>
+        <v>4.557263546727043</v>
       </c>
       <c r="B2">
-        <v>10.782033157584491</v>
+        <v>10.808804068452179</v>
       </c>
       <c r="C2">
         <v>265.01886677730067</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>3.89018224264694</v>
+        <v>3.8475507562259046</v>
       </c>
       <c r="B3">
-        <v>10.435093943733889</v>
+        <v>10.488066269957713</v>
       </c>
       <c r="C3">
         <v>265.01886677730067</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>3.2491891564755835</v>
+        <v>3.1804061937667596</v>
       </c>
       <c r="B4">
-        <v>10.063284344943769</v>
+        <v>10.137262996982546</v>
       </c>
       <c r="C4">
         <v>265.01886677730067</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2.6352385029570971</v>
+        <v>2.5447849231008188</v>
       </c>
       <c r="B5">
-        <v>9.6726433948421437</v>
+        <v>9.76419516735209</v>
       </c>
       <c r="C5">
         <v>265.01886677730067</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>2.0447010446387095</v>
+        <v>1.9360915197964785</v>
       </c>
       <c r="B6">
-        <v>9.2656983603485017</v>
+        <v>9.3721084791452061</v>
       </c>
       <c r="C6">
         <v>265.01886677730067</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>1.475450616265001</v>
+        <v>1.3516490582344667</v>
       </c>
       <c r="B7">
-        <v>8.8439298244187121</v>
+        <v>8.9628936156859353</v>
       </c>
       <c r="C7">
         <v>265.01886677730067</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>0.92618335788490636</v>
+        <v>0.7898305607645</v>
       </c>
       <c r="B8">
-        <v>8.4082457469658021</v>
+        <v>8.5376996935167124</v>
       </c>
       <c r="C8">
         <v>265.01886677730067</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>0.39495837344958196</v>
+        <v>0.24818877459298469</v>
       </c>
       <c r="B9">
-        <v>7.95999769631293</v>
+        <v>8.0982551805535845</v>
       </c>
       <c r="C9">
         <v>265.01886677730067</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>-0.12030185190736774</v>
+        <v>-0.275900727892622</v>
       </c>
       <c r="B10">
-        <v>7.5006323770819172</v>
+        <v>7.6464136813518939</v>
       </c>
       <c r="C10">
         <v>265.01886677730067</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>-0.62158427222477541</v>
+        <v>-0.78495079843736348</v>
       </c>
       <c r="B11">
-        <v>7.0315334306790351</v>
+        <v>7.1839499956505382</v>
       </c>
       <c r="C11">
         <v>265.01886677730067</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>-1.1099900612172282</v>
+        <v>-1.2803427892952544</v>
       </c>
       <c r="B12">
-        <v>6.5534676738082629</v>
+        <v>6.7118397574576081</v>
       </c>
       <c r="C12">
         <v>265.01886677730067</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-1.5831678321299123</v>
+        <v>-1.7590436306236705</v>
       </c>
       <c r="B13">
-        <v>6.064797687579909</v>
+        <v>6.2279407426743791</v>
       </c>
       <c r="C13">
         <v>265.01886677730067</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-2.0397373483476318</v>
+        <v>-2.2192650166227792</v>
       </c>
       <c r="B14">
-        <v>5.5645623261929478</v>
+        <v>5.7309898904486243</v>
       </c>
       <c r="C14">
         <v>265.01886677730067</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-2.4856555342830875</v>
+        <v>-2.6686121197605486</v>
       </c>
       <c r="B15">
-        <v>5.0569097717947331</v>
+        <v>5.2263586510209175</v>
       </c>
       <c r="C15">
         <v>265.01886677730067</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.9263856090772169</v>
+        <v>-3.1140599265966205</v>
       </c>
       <c r="B16">
-        <v>4.5456444084159262</v>
+        <v>4.7189733812084915</v>
       </c>
       <c r="C16">
         <v>265.01886677730067</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.3580788097560421</v>
+        <v>-3.5506692017895705</v>
       </c>
       <c r="B17">
-        <v>4.0280860996720413</v>
+        <v>4.2053455530424246</v>
       </c>
       <c r="C17">
         <v>265.01886677730067</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-3.775744468535263</v>
+        <v>-3.9720413882679741</v>
       </c>
       <c r="B18">
-        <v>3.5007595288439339</v>
+        <v>3.6809559355565069</v>
       </c>
       <c r="C18">
         <v>265.01886677730067</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-4.1791362805042436</v>
+        <v>-4.3778548639415158</v>
       </c>
       <c r="B19">
-        <v>2.9634931782888851</v>
+        <v>3.1455773705815231</v>
       </c>
       <c r="C19">
         <v>265.01886677730067</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-4.5691940314707633</v>
+        <v>-4.769307240465162</v>
       </c>
       <c r="B20">
-        <v>2.4169414801332825</v>
+        <v>2.600055718147503</v>
       </c>
       <c r="C20">
         <v>265.01886677730067</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-4.9468575072425969</v>
+        <v>-5.14759612949387</v>
       </c>
       <c r="B21">
-        <v>1.8617588665035236</v>
+        <v>2.0452368382844832</v>
       </c>
       <c r="C21">
         <v>265.01886677730067</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-5.3128966194156257</v>
+        <v>-5.5137034022366924</v>
       </c>
       <c r="B22">
-        <v>1.298481475398982</v>
+        <v>1.4818142159021439</v>
       </c>
       <c r="C22">
         <v>265.01886677730067</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.6674017827381391</v>
+        <v>-5.8677479681190423</v>
       </c>
       <c r="B23">
-        <v>0.72717226831097836</v>
+        <v>0.90987183542876959</v>
       </c>
       <c r="C23">
         <v>265.01886677730067</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-6.0102935377465281</v>
+        <v>-6.2096329961204155</v>
       </c>
       <c r="B24">
-        <v>0.14777591260382253</v>
+        <v>0.32934130617229751</v>
       </c>
       <c r="C24">
         <v>265.01886677730067</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-6.3414924249771838</v>
+        <v>-6.5392616552203169</v>
       </c>
       <c r="B25">
-        <v>-0.43976292435817921</v>
+        <v>-0.25984576255933889</v>
       </c>
       <c r="C25">
         <v>265.01886677730067</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-6.66088625390502</v>
+        <v>-6.8564968715021113</v>
       </c>
       <c r="B26">
-        <v>-1.0355223679130379</v>
+        <v>-0.85778618457615186</v>
       </c>
       <c r="C26">
         <v>265.01886677730067</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-6.9682319097590408</v>
+        <v>-7.1610405994646742</v>
       </c>
       <c r="B27">
-        <v>-1.6396717142080617</v>
+        <v>-1.4646904661599616</v>
       </c>
       <c r="C27">
         <v>265.01886677730067</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-7.263253546706764</v>
+        <v>-7.4525545507107376</v>
       </c>
       <c r="B28">
-        <v>-2.2524030520928604</v>
+        <v>-2.0807975367105214</v>
       </c>
       <c r="C28">
         <v>265.01886677730067</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-7.5456753189157082</v>
+        <v>-7.7307004368430423</v>
       </c>
       <c r="B29">
-        <v>-2.8739084704170597</v>
+        <v>-2.7063463256275946</v>
       </c>
       <c r="C29">
         <v>265.01886677730067</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-7.8153373873965473</v>
+        <v>-7.9952902473877527</v>
       </c>
       <c r="B30">
-        <v>-3.504299275149318</v>
+        <v>-3.3414696226551577</v>
       </c>
       <c r="C30">
         <v>265.01886677730067</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-8.0725439405325439</v>
+        <v>-8.2467370835647351</v>
       </c>
       <c r="B31">
-        <v>-4.1433636407344512</v>
+        <v>-3.9858756589140394</v>
       </c>
       <c r="C31">
         <v>265.01886677730067</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-8.3177151735501145</v>
+        <v>-8.4856043245172916</v>
       </c>
       <c r="B32">
-        <v>-4.7908089587363225</v>
+        <v>-4.639166525869296</v>
       </c>
       <c r="C32">
         <v>265.01886677730067</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-8.5512712816756782</v>
+        <v>-8.7124553493887138</v>
       </c>
       <c r="B33">
-        <v>-5.4463426207187915</v>
+        <v>-5.3009443149859745</v>
       </c>
       <c r="C33">
         <v>265.01886677730067</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-8.7734270262609737</v>
+        <v>-8.92759288761631</v>
       </c>
       <c r="B34">
-        <v>-6.1098150748085107</v>
+        <v>-5.9709952117693019</v>
       </c>
       <c r="C34">
         <v>265.01886677730067</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-8.9835754331590678</v>
+        <v>-9.1302770698134612</v>
       </c>
       <c r="B35">
-        <v>-6.7816489953833692</v>
+        <v>-6.6498417778852339</v>
       </c>
       <c r="C35">
         <v>265.01886677730067</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-9.180904094348362</v>
+        <v>-9.3195073768875609</v>
       </c>
       <c r="B36">
-        <v>-7.462410113384041</v>
+        <v>-7.33819066903991</v>
       </c>
       <c r="C36">
         <v>265.01886677730067</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-9.3646006018072541</v>
+        <v>-9.49428328974601</v>
       </c>
       <c r="B37">
-        <v>-8.1526641597512164</v>
+        <v>-8.0367485409394774</v>
       </c>
       <c r="C37">
         <v>265.01886677730067</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-9.53335931069306</v>
+        <v>-9.6529755437447431</v>
       </c>
       <c r="B38">
-        <v>-8.85332033733052</v>
+        <v>-8.7466661254050937</v>
       </c>
       <c r="C38">
         <v>265.01886677730067</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-9.6839016288787647</v>
+        <v>-9.79143989203388</v>
       </c>
       <c r="B39">
-        <v>-9.5666617365873527</v>
+        <v>-9.4708704587179966</v>
       </c>
       <c r="C39">
         <v>265.01886677730067</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-9.8124557274162623</v>
+        <v>-9.9049033422120818</v>
       </c>
       <c r="B40">
-        <v>-10.295314919892054</v>
+        <v>-10.212732653274435</v>
       </c>
       <c r="C40">
         <v>265.01886677730067</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-9.9152497773574577</v>
+        <v>-9.98859290187801</v>
       </c>
       <c r="B41">
-        <v>-11.041906449614965</v>
+        <v>-10.975623821470666</v>
       </c>
       <c r="C41">
         <v>265.01886677730067</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-9.9152497773574577</v>
+        <v>-9.98859290187801</v>
       </c>
       <c r="B42">
-        <v>-11.041906449614965</v>
+        <v>-10.975623821470666</v>
       </c>
       <c r="C42">
         <v>265.01886677730067</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-9.6431804975974718</v>
+        <v>-9.688276944659556</v>
       </c>
       <c r="B43">
-        <v>-10.413191937909319</v>
+        <v>-10.365733511591492</v>
       </c>
       <c r="C43">
         <v>265.01886677730067</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-9.3744228512031444</v>
+        <v>-9.3953909674594112</v>
       </c>
       <c r="B44">
-        <v>-9.7821713270400323</v>
+        <v>-9.7505954879852546</v>
       </c>
       <c r="C44">
         <v>265.01886677730067</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-9.1055842565613787</v>
+        <v>-9.10553945969049</v>
       </c>
       <c r="B45">
-        <v>-9.1512070855405074</v>
+        <v>-9.1333142517661479</v>
       </c>
       <c r="C45">
         <v>265.01886677730067</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-8.833272132059081</v>
+        <v>-8.814326910765713</v>
       </c>
       <c r="B46">
-        <v>-8.5226616819441539</v>
+        <v>-8.5169943040483691</v>
       </c>
       <c r="C46">
         <v>265.01886677730067</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-8.5545698053218864</v>
+        <v>-8.5179693087326829</v>
       </c>
       <c r="B47">
-        <v>-7.8985661791678048</v>
+        <v>-7.904308251140014</v>
       </c>
       <c r="C47">
         <v>265.01886677730067</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-8.2684642409303937</v>
+        <v>-8.2151286361777647</v>
       </c>
       <c r="B48">
-        <v>-7.2796260176619816</v>
+        <v>-7.29620112012477</v>
       </c>
       <c r="C48">
         <v>265.01886677730067</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-7.9744183127039205</v>
+        <v>-7.9050783743220139</v>
       </c>
       <c r="B49">
-        <v>-6.6662152322606278</v>
+        <v>-6.6931860432802246</v>
       </c>
       <c r="C49">
         <v>265.01886677730067</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-7.6718948944618006</v>
+        <v>-7.5870920043864789</v>
       </c>
       <c r="B50">
-        <v>-6.0587078577976961</v>
+        <v>-6.0957761528839676</v>
       </c>
       <c r="C50">
         <v>265.01886677730067</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-7.3605464705637527</v>
+        <v>-7.2606879076267381</v>
       </c>
       <c r="B51">
-        <v>-5.4573458913298909</v>
+        <v>-5.5043116109943231</v>
       </c>
       <c r="C51">
         <v>265.01886677730067</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-7.0407839675310822</v>
+        <v>-6.9263640654364469</v>
       </c>
       <c r="B52">
-        <v>-4.8618431788049872</v>
+        <v>-4.9184406987925549</v>
       </c>
       <c r="C52">
         <v>265.01886677730067</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-6.7132079224254859</v>
+        <v>-6.5848633592437835</v>
       </c>
       <c r="B53">
-        <v>-4.2717815283935181</v>
+        <v>-4.3376387272406562</v>
       </c>
       <c r="C53">
         <v>265.01886677730067</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-6.3784188723086563</v>
+        <v>-6.23692867047692</v>
       </c>
       <c r="B54">
-        <v>-3.6867427482660062</v>
+        <v>-3.7613810073006126</v>
       </c>
       <c r="C54">
         <v>265.01886677730067</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-6.0368885434678194</v>
+        <v>-5.8831398583157855</v>
       </c>
       <c r="B55">
-        <v>-3.10639834565882</v>
+        <v>-3.18925799076762</v>
       </c>
       <c r="C55">
         <v>265.01886677730067</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-5.6885734190923207</v>
+        <v>-5.5234246929473185</v>
       </c>
       <c r="B56">
-        <v>-2.5307786240716452</v>
+        <v>-2.6213206927696553</v>
       </c>
       <c r="C56">
         <v>265.01886677730067</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-5.3333011715970269</v>
+        <v>-5.1575479223102079</v>
       </c>
       <c r="B57">
-        <v>-1.9600035860699978</v>
+        <v>-2.05773526926789</v>
       </c>
       <c r="C57">
         <v>265.01886677730067</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-4.970899473396817</v>
+        <v>-4.7852742943431492</v>
       </c>
       <c r="B58">
-        <v>-1.3941932342194057</v>
+        <v>-1.4986678762235075</v>
       </c>
       <c r="C58">
         <v>265.01886677730067</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-4.6012171662283823</v>
+        <v>-4.406397291964991</v>
       </c>
       <c r="B59">
-        <v>-0.8334528295515311</v>
+        <v>-0.94426437439506772</v>
       </c>
       <c r="C59">
         <v>265.01886677730067</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.2241877691157024</v>
+        <v>-4.0208253380152312</v>
       </c>
       <c r="B60">
-        <v>-0.2778286669626604</v>
+        <v>-0.39458944373071114</v>
       </c>
       <c r="C60">
         <v>265.01886677730067</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-3.8397659704045854</v>
+        <v>-3.6284955903135252</v>
       </c>
       <c r="B61">
-        <v>0.27264770018477064</v>
+        <v>0.15031253102403105</v>
       </c>
       <c r="C61">
         <v>265.01886677730067</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.4479064584408348</v>
+        <v>-3.2293452066795361</v>
       </c>
       <c r="B62">
-        <v>0.8179447185283234</v>
+        <v>0.69039716512362537</v>
       </c>
       <c r="C62">
         <v>265.01886677730067</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.04872217427615</v>
+        <v>-2.8235155179747493</v>
       </c>
       <c r="B63">
-        <v>1.3581410360450239</v>
+        <v>1.2257642790117407</v>
       </c>
       <c r="C63">
         <v>265.01886677730067</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.642959069785797</v>
+        <v>-2.4119645472279632</v>
       </c>
       <c r="B64">
-        <v>1.8937561060697521</v>
+        <v>1.7570905138888537</v>
       </c>
       <c r="C64">
         <v>265.01886677730067</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.2315213495509432</v>
+        <v>-1.99585449050981</v>
       </c>
       <c r="B65">
-        <v>2.42541958327684</v>
+        <v>2.2851967161446325</v>
       </c>
       <c r="C65">
         <v>265.01886677730067</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.8153132181527467</v>
+        <v>-1.5763475438909154</v>
       </c>
       <c r="B66">
-        <v>2.9537611223406288</v>
+        <v>2.8109037321687547</v>
       </c>
       <c r="C66">
         <v>265.01886677730067</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.3940432304300381</v>
+        <v>-1.1530771551731056</v>
       </c>
       <c r="B67">
-        <v>3.4785777716151456</v>
+        <v>3.3339526701476063</v>
       </c>
       <c r="C67">
         <v>265.01886677730067</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.96263734225231556</v>
+        <v>-0.71956177908299523</v>
       </c>
       <c r="B68">
-        <v>3.9963361541731635</v>
+        <v>3.8497656854544298</v>
       </c>
       <c r="C68">
         <v>265.01886677730067</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.51714930088718214</v>
+        <v>-0.27076514436754318</v>
       </c>
       <c r="B69">
-        <v>4.5042882453631465</v>
+        <v>4.35478571471589</v>
       </c>
       <c r="C69">
         <v>265.01886677730067</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>-0.062926618164025214</v>
+        <v>0.18645293106966465</v>
       </c>
       <c r="B70">
-        <v>5.006157854917535</v>
+        <v>4.8538577723854646</v>
       </c>
       <c r="C70">
         <v>265.01886677730067</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>0.39420090279951042</v>
+        <v>0.64461380426438863</v>
       </c>
       <c r="B71">
-        <v>5.5060046424089135</v>
+        <v>5.3522639422973644</v>
       </c>
       <c r="C71">
         <v>265.01886677730067</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.85576805829453917</v>
+        <v>1.1056596211663885</v>
       </c>
       <c r="B72">
-        <v>6.0027598323864755</v>
+        <v>5.848632507981911</v>
       </c>
       <c r="C72">
         <v>265.01886677730067</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>1.3242945450088981</v>
+        <v>1.5727909780133611</v>
       </c>
       <c r="B73">
-        <v>6.4946688011395395</v>
+        <v>6.3407029232774779</v>
       </c>
       <c r="C73">
         <v>265.01886677730067</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.79887506180858</v>
+        <v>2.0448214832807605</v>
       </c>
       <c r="B74">
-        <v>6.9823619669413457</v>
+        <v>6.8293131235585456</v>
       </c>
       <c r="C74">
         <v>265.01886677730067</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2.27773300875073</v>
+        <v>2.5194476600521978</v>
       </c>
       <c r="B75">
-        <v>7.4670764883749792</v>
+        <v>7.3160900294096</v>
       </c>
       <c r="C75">
         <v>265.01886677730067</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.7590315884789431</v>
+        <v>2.994284677606148</v>
       </c>
       <c r="B76">
-        <v>7.9500914432789775</v>
+        <v>7.8027180207190412</v>
       </c>
       <c r="C76">
         <v>265.01886677730067</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>3.2410870774813056</v>
+        <v>3.4671412584634314</v>
       </c>
       <c r="B77">
-        <v>8.4325793145202219</v>
+        <v>8.2907447728344437</v>
       </c>
       <c r="C77">
         <v>265.01886677730067</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>3.7228882450374194</v>
+        <v>3.9366816919193708</v>
       </c>
       <c r="B78">
-        <v>8.9152442858234977</v>
+        <v>8.7811136836361552</v>
       </c>
       <c r="C78">
         <v>265.01886677730067</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>4.2026182920864192</v>
+        <v>4.4005369783481294</v>
       </c>
       <c r="B79">
-        <v>9.3993515089529556</v>
+        <v>9.2754979516826168</v>
       </c>
       <c r="C79">
         <v>265.01886677730067</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>4.67699269436462</v>
+        <v>4.8544548017542191</v>
       </c>
       <c r="B80">
-        <v>9.88718820529487</v>
+        <v>9.77690094131214</v>
       </c>
       <c r="C80">
         <v>265.01886677730067</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>5.1377132789711126</v>
+        <v>5.2877625601495453</v>
       </c>
       <c r="B81">
-        <v>10.384532915971869</v>
+        <v>10.292860594728923</v>
       </c>
       <c r="C81">
         <v>265.01886677730067</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5.4322498988055763</v>
+        <v>5.5052051078294371</v>
       </c>
       <c r="B82">
-        <v>10.99760200186067</v>
+        <v>10.961283488514393</v>
       </c>
       <c r="C82">
         <v>265.01886677730067</v>
